--- a/Excel/Excel Workbook/Excel Data Analysis.xlsx
+++ b/Excel/Excel Workbook/Excel Data Analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1194DEB9-14A9-4A71-98FC-BEE9BB7E1FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206459B7-1D62-43B0-A7E4-DFBE7F91BEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Sort (text)" sheetId="1" r:id="rId1"/>
@@ -288,10 +288,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -816,170 +815,170 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>525</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="1">
         <v>534</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="1">
         <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="1">
         <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="1">
         <v>530</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="1">
         <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="1">
         <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="1">
         <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="1">
         <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="1">
         <v>395</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="1">
         <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="1">
         <v>349</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="1">
         <v>479</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="1">
         <v>253</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="1">
         <v>413</v>
       </c>
     </row>
@@ -992,6 +991,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D21887AB-7AEF-4113-B69A-3ED1BD5E9218}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="17.1796875" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">

--- a/Excel/Excel Workbook/Excel Data Analysis.xlsx
+++ b/Excel/Excel Workbook/Excel Data Analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206459B7-1D62-43B0-A7E4-DFBE7F91BEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227AAC47-8D3E-4D3F-9E0A-963B2636DA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Example Sort (text)" sheetId="1" r:id="rId1"/>

--- a/Excel/Excel Workbook/Excel Data Analysis.xlsx
+++ b/Excel/Excel Workbook/Excel Data Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227AAC47-8D3E-4D3F-9E0A-963B2636DA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9C9D0B-BF89-4DBC-822F-F14E89004905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="5" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
